--- a/SuppXLS/Scen_TSParameters_ts_04.xlsx
+++ b/SuppXLS/Scen_TSParameters_ts_04.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VS_CEA_8C\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD856075-7840-4667-A201-7FDFA4C66908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6FAC49-4F1D-43DC-B8D7-FAE21E52BE8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" firstSheet="21" activeTab="25" xr2:uid="{9AFE621A-5A4D-4021-A892-D7746615649C}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12773" firstSheet="21" activeTab="25" xr2:uid="{7A28BDD6-2517-4150-AD45-0577014C080B}"/>
   </bookViews>
   <sheets>
     <sheet name="resource_profiles_FRA" sheetId="2" r:id="rId1"/>
@@ -2565,13 +2565,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S1aH2,S2aH2</t>
+    <t>S2aH2,S1aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S1aH1,S2aH1</t>
+    <t>S2aH1,S1aH1</t>
   </si>
   <si>
     <t>share of charging at night</t>
@@ -2812,9 +2812,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="3"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Heading 2 2" xfId="2" xr:uid="{95B1ADFF-5D94-460A-813D-6ED6DC51B6AC}"/>
-    <cellStyle name="Heading 3 2" xfId="3" xr:uid="{0490DD74-AA8E-4344-A9E9-1CD509804894}"/>
-    <cellStyle name="Input 2" xfId="1" xr:uid="{59B1F941-B3E0-435A-AD7B-8A54BC2D7BB0}"/>
+    <cellStyle name="Heading 2 2" xfId="2" xr:uid="{8A863142-3873-42D5-BEA7-664B891DF33A}"/>
+    <cellStyle name="Heading 3 2" xfId="3" xr:uid="{A6A6F716-3C14-402B-952B-C6A5C98DF5D0}"/>
+    <cellStyle name="Input 2" xfId="1" xr:uid="{7FCE75A9-DF23-45DF-AB16-19A6743572E4}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3126,7 +3126,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A20EA549-6D6A-4819-B347-BE20E8947B10}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC89D46B-48AC-415A-A9F8-EEBF7477E1A1}">
   <dimension ref="B9:O130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7028,7 +7028,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76DC6BB8-0015-4CD0-B360-442303CE1953}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9ABB249-E779-4EC2-8978-84E5C924FEA2}">
   <dimension ref="B9:O102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9914,7 +9914,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5F7563B-D7CB-450E-9A5A-B96B3A606E5C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817B4C15-8098-47C6-B2E3-5EA49803E987}">
   <dimension ref="B9:AF65"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12722,7 +12722,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F10B999-A5E6-4F19-B9F5-9E65A91EEE70}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{805204B5-FE71-4F91-A64B-00E3F5931147}">
   <dimension ref="A9:S68"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12949,7 +12949,7 @@
         <v>180</v>
       </c>
       <c r="R14">
-        <v>0.41848333333333332</v>
+        <v>0.41848333333333337</v>
       </c>
       <c r="S14" t="s">
         <v>179</v>
@@ -12969,7 +12969,7 @@
         <v>178</v>
       </c>
       <c r="R15">
-        <v>0.37261666666666665</v>
+        <v>0.3726166666666666</v>
       </c>
       <c r="S15" t="s">
         <v>179</v>
@@ -13029,7 +13029,7 @@
         <v>180</v>
       </c>
       <c r="R18">
-        <v>0.45290000000000002</v>
+        <v>0.45289999999999991</v>
       </c>
       <c r="S18" t="s">
         <v>179</v>
@@ -13043,7 +13043,7 @@
         <v>178</v>
       </c>
       <c r="R19">
-        <v>0.45583333333333331</v>
+        <v>0.45583333333333337</v>
       </c>
       <c r="S19" t="s">
         <v>179</v>
@@ -13057,7 +13057,7 @@
         <v>180</v>
       </c>
       <c r="R20">
-        <v>0.46934999999999999</v>
+        <v>0.46934999999999993</v>
       </c>
       <c r="S20" t="s">
         <v>179</v>
@@ -13071,7 +13071,7 @@
         <v>178</v>
       </c>
       <c r="R21">
-        <v>0.47668333333333329</v>
+        <v>0.47668333333333335</v>
       </c>
       <c r="S21" t="s">
         <v>179</v>
@@ -13085,7 +13085,7 @@
         <v>180</v>
       </c>
       <c r="R22">
-        <v>0.51294999999999991</v>
+        <v>0.51295000000000002</v>
       </c>
       <c r="S22" t="s">
         <v>179</v>
@@ -13099,7 +13099,7 @@
         <v>178</v>
       </c>
       <c r="R23">
-        <v>0.47573333333333329</v>
+        <v>0.47573333333333334</v>
       </c>
       <c r="S23" t="s">
         <v>179</v>
@@ -13127,7 +13127,7 @@
         <v>178</v>
       </c>
       <c r="R25">
-        <v>0.48191666666666672</v>
+        <v>0.4819166666666666</v>
       </c>
       <c r="S25" t="s">
         <v>179</v>
@@ -13141,7 +13141,7 @@
         <v>180</v>
       </c>
       <c r="R26">
-        <v>0.46286666666666676</v>
+        <v>0.46286666666666659</v>
       </c>
       <c r="S26" t="s">
         <v>179</v>
@@ -13253,7 +13253,7 @@
         <v>180</v>
       </c>
       <c r="R34">
-        <v>0.47205000000000008</v>
+        <v>0.47205000000000003</v>
       </c>
       <c r="S34" t="s">
         <v>179</v>
@@ -13323,7 +13323,7 @@
         <v>178</v>
       </c>
       <c r="R39">
-        <v>0.46954999999999997</v>
+        <v>0.46955000000000008</v>
       </c>
       <c r="S39" t="s">
         <v>179</v>
@@ -13351,7 +13351,7 @@
         <v>178</v>
       </c>
       <c r="R41">
-        <v>0.46523333333333333</v>
+        <v>0.46523333333333339</v>
       </c>
       <c r="S41" t="s">
         <v>179</v>
@@ -13393,7 +13393,7 @@
         <v>180</v>
       </c>
       <c r="R44">
-        <v>0.49419999999999997</v>
+        <v>0.49420000000000003</v>
       </c>
       <c r="S44" t="s">
         <v>179</v>
@@ -13421,7 +13421,7 @@
         <v>180</v>
       </c>
       <c r="R46">
-        <v>0.58230000000000004</v>
+        <v>0.58229999999999993</v>
       </c>
       <c r="S46" t="s">
         <v>179</v>
@@ -13477,7 +13477,7 @@
         <v>180</v>
       </c>
       <c r="R50">
-        <v>0.49183333333333334</v>
+        <v>0.49183333333333329</v>
       </c>
       <c r="S50" t="s">
         <v>179</v>
@@ -13505,7 +13505,7 @@
         <v>180</v>
       </c>
       <c r="R52">
-        <v>0.51386666666666658</v>
+        <v>0.51386666666666669</v>
       </c>
       <c r="S52" t="s">
         <v>179</v>
@@ -13519,7 +13519,7 @@
         <v>178</v>
       </c>
       <c r="R53">
-        <v>0.45556666666666662</v>
+        <v>0.45556666666666668</v>
       </c>
       <c r="S53" t="s">
         <v>179</v>
@@ -13575,7 +13575,7 @@
         <v>178</v>
       </c>
       <c r="R57">
-        <v>0.37401666666666666</v>
+        <v>0.37401666666666672</v>
       </c>
       <c r="S57" t="s">
         <v>179</v>
@@ -13659,7 +13659,7 @@
         <v>178</v>
       </c>
       <c r="R63">
-        <v>0.3878833333333333</v>
+        <v>0.38788333333333336</v>
       </c>
       <c r="S63" t="s">
         <v>179</v>
@@ -13673,7 +13673,7 @@
         <v>180</v>
       </c>
       <c r="R64">
-        <v>0.39210000000000006</v>
+        <v>0.39209999999999995</v>
       </c>
       <c r="S64" t="s">
         <v>179</v>
@@ -13741,7 +13741,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{455FA9F3-D113-4BCD-9415-3CD690725829}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B8FF2EB-7D24-48F0-B344-F9374DE2B9A6}">
   <dimension ref="B9:J50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14635,7 +14635,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1499080-158A-41B5-9540-3F4C9DB2C1C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB42DD7-6D30-430F-8086-C98537A1B311}">
   <dimension ref="B9:AF26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15574,7 +15574,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA08914-06D5-487B-9A1D-CF87DB6F45DD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{158B8AC9-20FF-4C9B-BF61-68DEAAA819E6}">
   <dimension ref="A9:S68"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15881,7 +15881,7 @@
         <v>180</v>
       </c>
       <c r="R18">
-        <v>0.32868333333333338</v>
+        <v>0.32868333333333327</v>
       </c>
       <c r="S18" t="s">
         <v>179</v>
@@ -15909,7 +15909,7 @@
         <v>180</v>
       </c>
       <c r="R20">
-        <v>0.32941666666666669</v>
+        <v>0.32941666666666664</v>
       </c>
       <c r="S20" t="s">
         <v>179</v>
@@ -16021,7 +16021,7 @@
         <v>180</v>
       </c>
       <c r="R28">
-        <v>0.39328333333333337</v>
+        <v>0.39328333333333326</v>
       </c>
       <c r="S28" t="s">
         <v>179</v>
@@ -16105,7 +16105,7 @@
         <v>180</v>
       </c>
       <c r="R34">
-        <v>0.37211666666666671</v>
+        <v>0.37211666666666665</v>
       </c>
       <c r="S34" t="s">
         <v>179</v>
@@ -16203,7 +16203,7 @@
         <v>178</v>
       </c>
       <c r="R41">
-        <v>0.23129999999999998</v>
+        <v>0.23130000000000003</v>
       </c>
       <c r="S41" t="s">
         <v>179</v>
@@ -16329,7 +16329,7 @@
         <v>180</v>
       </c>
       <c r="R50">
-        <v>0.28736666666666666</v>
+        <v>0.28736666666666671</v>
       </c>
       <c r="S50" t="s">
         <v>179</v>
@@ -16357,7 +16357,7 @@
         <v>180</v>
       </c>
       <c r="R52">
-        <v>0.28331666666666672</v>
+        <v>0.28331666666666666</v>
       </c>
       <c r="S52" t="s">
         <v>179</v>
@@ -16399,7 +16399,7 @@
         <v>178</v>
       </c>
       <c r="R55">
-        <v>0.20871666666666663</v>
+        <v>0.20871666666666666</v>
       </c>
       <c r="S55" t="s">
         <v>179</v>
@@ -16441,7 +16441,7 @@
         <v>180</v>
       </c>
       <c r="R58">
-        <v>0.30238333333333328</v>
+        <v>0.30238333333333334</v>
       </c>
       <c r="S58" t="s">
         <v>179</v>
@@ -16469,7 +16469,7 @@
         <v>180</v>
       </c>
       <c r="R60">
-        <v>0.33388333333333331</v>
+        <v>0.33388333333333337</v>
       </c>
       <c r="S60" t="s">
         <v>179</v>
@@ -16511,7 +16511,7 @@
         <v>178</v>
       </c>
       <c r="R63">
-        <v>0.25925000000000004</v>
+        <v>0.25924999999999998</v>
       </c>
       <c r="S63" t="s">
         <v>179</v>
@@ -16581,7 +16581,7 @@
         <v>180</v>
       </c>
       <c r="R68">
-        <v>0.31170000000000003</v>
+        <v>0.31169999999999992</v>
       </c>
       <c r="S68" t="s">
         <v>179</v>
@@ -16593,7 +16593,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31C79101-D306-440F-9F77-223E443E4F23}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A8B80D-8B30-4DD5-AE2D-4CB1BF261764}">
   <dimension ref="B9:O106"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19871,7 +19871,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7897F32-4724-48EB-9222-253B4A4EFB7F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{976BE21E-2FF9-4154-97F7-F03AB2063D36}">
   <dimension ref="B9:AF73"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23055,7 +23055,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F70FFB74-3A38-4C7A-8F34-3217491A447B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12476787-9B6C-42C9-92B2-3F19AB327633}">
   <dimension ref="A9:S68"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23159,7 +23159,7 @@
         <v>178</v>
       </c>
       <c r="R11">
-        <v>0.2375666666666667</v>
+        <v>0.23756666666666668</v>
       </c>
       <c r="S11" t="s">
         <v>179</v>
@@ -23376,7 +23376,7 @@
         <v>178</v>
       </c>
       <c r="R19">
-        <v>0.28516666666666662</v>
+        <v>0.28516666666666668</v>
       </c>
       <c r="S19" t="s">
         <v>179</v>
@@ -23390,7 +23390,7 @@
         <v>180</v>
       </c>
       <c r="R20">
-        <v>0.36970000000000008</v>
+        <v>0.36969999999999997</v>
       </c>
       <c r="S20" t="s">
         <v>179</v>
@@ -23446,7 +23446,7 @@
         <v>180</v>
       </c>
       <c r="R24">
-        <v>0.34466666666666662</v>
+        <v>0.34466666666666668</v>
       </c>
       <c r="S24" t="s">
         <v>179</v>
@@ -23474,7 +23474,7 @@
         <v>180</v>
       </c>
       <c r="R26">
-        <v>0.32903333333333329</v>
+        <v>0.32903333333333334</v>
       </c>
       <c r="S26" t="s">
         <v>179</v>
@@ -23600,7 +23600,7 @@
         <v>178</v>
       </c>
       <c r="R35">
-        <v>0.25191666666666668</v>
+        <v>0.25191666666666673</v>
       </c>
       <c r="S35" t="s">
         <v>179</v>
@@ -23726,7 +23726,7 @@
         <v>180</v>
       </c>
       <c r="R44">
-        <v>0.31986666666666669</v>
+        <v>0.31986666666666663</v>
       </c>
       <c r="S44" t="s">
         <v>179</v>
@@ -23740,7 +23740,7 @@
         <v>178</v>
       </c>
       <c r="R45">
-        <v>0.2708666666666667</v>
+        <v>0.27086666666666664</v>
       </c>
       <c r="S45" t="s">
         <v>179</v>
@@ -23796,7 +23796,7 @@
         <v>178</v>
       </c>
       <c r="R49">
-        <v>0.23861666666666662</v>
+        <v>0.23861666666666667</v>
       </c>
       <c r="S49" t="s">
         <v>179</v>
@@ -23838,7 +23838,7 @@
         <v>180</v>
       </c>
       <c r="R52">
-        <v>0.31853333333333339</v>
+        <v>0.31853333333333333</v>
       </c>
       <c r="S52" t="s">
         <v>179</v>
@@ -23866,7 +23866,7 @@
         <v>180</v>
       </c>
       <c r="R54">
-        <v>0.29258333333333336</v>
+        <v>0.29258333333333331</v>
       </c>
       <c r="S54" t="s">
         <v>179</v>
@@ -23936,7 +23936,7 @@
         <v>178</v>
       </c>
       <c r="R59">
-        <v>0.23073333333333335</v>
+        <v>0.23073333333333332</v>
       </c>
       <c r="S59" t="s">
         <v>179</v>
@@ -23978,7 +23978,7 @@
         <v>180</v>
       </c>
       <c r="R62">
-        <v>0.27383333333333337</v>
+        <v>0.27383333333333332</v>
       </c>
       <c r="S62" t="s">
         <v>179</v>
@@ -24048,7 +24048,7 @@
         <v>178</v>
       </c>
       <c r="R67">
-        <v>0.22486666666666666</v>
+        <v>0.22486666666666669</v>
       </c>
       <c r="S67" t="s">
         <v>179</v>
@@ -24074,7 +24074,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E0FACEB-AF01-4882-883E-0AB8CA77733C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{481BCA01-2A70-4777-A363-4F9B7D47BD0E}">
   <dimension ref="B9:O114"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27704,7 +27704,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{716CAB51-576C-44C3-8668-E8AC232E2FD4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8FA189F-3E91-4B45-ADA2-BF1663AA294A}">
   <dimension ref="B9:AF85"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31452,7 +31452,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4310644B-39DA-4B7E-B9C1-A85ED0D991EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD11CFC9-7866-40B2-AAB5-B417EE88AE81}">
   <dimension ref="B9:AF80"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -34965,7 +34965,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B806900-3B0E-418E-AE78-BA2C4F857409}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4D355D6-821B-4BE1-891F-65E8EF8CE20D}">
   <dimension ref="A9:S18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -35192,7 +35192,7 @@
         <v>180</v>
       </c>
       <c r="R14">
-        <v>0.14954999999999999</v>
+        <v>0.14955000000000002</v>
       </c>
       <c r="S14" t="s">
         <v>179</v>
@@ -35260,7 +35260,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32AD4E3B-6F53-40AB-B6F3-5DAE46DC3EE9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{775136AD-9570-465E-A3F2-9125DA3FF0FA}">
   <dimension ref="B9:O50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -36602,7 +36602,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B75111-8DC0-4A5A-AB40-24F58A3B16B2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D7B6CF4-20C4-49AE-8D90-F3812080617F}">
   <dimension ref="B9:AF35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -38000,7 +38000,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69CA7328-F4E1-49CB-9749-30072718C115}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B66DEAB1-C0FF-4803-9533-1EBE15A3AD3E}">
   <dimension ref="A9:S68"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -38104,7 +38104,7 @@
         <v>178</v>
       </c>
       <c r="R11">
-        <v>0.22586666666666669</v>
+        <v>0.22586666666666666</v>
       </c>
       <c r="S11" t="s">
         <v>179</v>
@@ -38247,7 +38247,7 @@
         <v>178</v>
       </c>
       <c r="R15">
-        <v>0.23186666666666667</v>
+        <v>0.23186666666666669</v>
       </c>
       <c r="S15" t="s">
         <v>179</v>
@@ -38335,7 +38335,7 @@
         <v>180</v>
       </c>
       <c r="R20">
-        <v>0.115</v>
+        <v>0.11499999999999999</v>
       </c>
       <c r="S20" t="s">
         <v>179</v>
@@ -38377,7 +38377,7 @@
         <v>178</v>
       </c>
       <c r="R23">
-        <v>0.48060000000000008</v>
+        <v>0.48059999999999997</v>
       </c>
       <c r="S23" t="s">
         <v>179</v>
@@ -38447,7 +38447,7 @@
         <v>180</v>
       </c>
       <c r="R28">
-        <v>0.10156666666666665</v>
+        <v>0.10156666666666668</v>
       </c>
       <c r="S28" t="s">
         <v>179</v>
@@ -38475,7 +38475,7 @@
         <v>180</v>
       </c>
       <c r="R30">
-        <v>0.10704999999999999</v>
+        <v>0.10705000000000002</v>
       </c>
       <c r="S30" t="s">
         <v>179</v>
@@ -38503,7 +38503,7 @@
         <v>180</v>
       </c>
       <c r="R32">
-        <v>0.16228333333333336</v>
+        <v>0.16228333333333333</v>
       </c>
       <c r="S32" t="s">
         <v>179</v>
@@ -38545,7 +38545,7 @@
         <v>178</v>
       </c>
       <c r="R35">
-        <v>0.3935833333333334</v>
+        <v>0.39358333333333334</v>
       </c>
       <c r="S35" t="s">
         <v>179</v>
@@ -38559,7 +38559,7 @@
         <v>180</v>
       </c>
       <c r="R36">
-        <v>0.13281666666666669</v>
+        <v>0.13281666666666667</v>
       </c>
       <c r="S36" t="s">
         <v>179</v>
@@ -38573,7 +38573,7 @@
         <v>178</v>
       </c>
       <c r="R37">
-        <v>0.42278333333333329</v>
+        <v>0.42278333333333334</v>
       </c>
       <c r="S37" t="s">
         <v>179</v>
@@ -38587,7 +38587,7 @@
         <v>180</v>
       </c>
       <c r="R38">
-        <v>0.11691666666666668</v>
+        <v>0.11691666666666667</v>
       </c>
       <c r="S38" t="s">
         <v>179</v>
@@ -38643,7 +38643,7 @@
         <v>180</v>
       </c>
       <c r="R42">
-        <v>0.12263333333333332</v>
+        <v>0.12263333333333333</v>
       </c>
       <c r="S42" t="s">
         <v>179</v>
@@ -38671,7 +38671,7 @@
         <v>180</v>
       </c>
       <c r="R44">
-        <v>6.2933333333333327E-2</v>
+        <v>6.2933333333333341E-2</v>
       </c>
       <c r="S44" t="s">
         <v>179</v>
@@ -38699,7 +38699,7 @@
         <v>180</v>
       </c>
       <c r="R46">
-        <v>0.13058333333333336</v>
+        <v>0.1305833333333333</v>
       </c>
       <c r="S46" t="s">
         <v>179</v>
@@ -38727,7 +38727,7 @@
         <v>180</v>
       </c>
       <c r="R48">
-        <v>0.10343333333333336</v>
+        <v>0.10343333333333334</v>
       </c>
       <c r="S48" t="s">
         <v>179</v>
@@ -38783,7 +38783,7 @@
         <v>180</v>
       </c>
       <c r="R52">
-        <v>0.12691666666666665</v>
+        <v>0.12691666666666668</v>
       </c>
       <c r="S52" t="s">
         <v>179</v>
@@ -38797,7 +38797,7 @@
         <v>178</v>
       </c>
       <c r="R53">
-        <v>0.47873333333333329</v>
+        <v>0.4787333333333334</v>
       </c>
       <c r="S53" t="s">
         <v>179</v>
@@ -38811,7 +38811,7 @@
         <v>180</v>
       </c>
       <c r="R54">
-        <v>9.2399999999999996E-2</v>
+        <v>9.2400000000000024E-2</v>
       </c>
       <c r="S54" t="s">
         <v>179</v>
@@ -38825,7 +38825,7 @@
         <v>178</v>
       </c>
       <c r="R55">
-        <v>0.37184999999999996</v>
+        <v>0.37185000000000001</v>
       </c>
       <c r="S55" t="s">
         <v>179</v>
@@ -38839,7 +38839,7 @@
         <v>180</v>
       </c>
       <c r="R56">
-        <v>0.12590000000000001</v>
+        <v>0.12589999999999998</v>
       </c>
       <c r="S56" t="s">
         <v>179</v>
@@ -38895,7 +38895,7 @@
         <v>180</v>
       </c>
       <c r="R60">
-        <v>0.14016666666666669</v>
+        <v>0.14016666666666666</v>
       </c>
       <c r="S60" t="s">
         <v>179</v>
@@ -39019,7 +39019,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E9B39CE-8038-4D02-8DEC-1A4072494D4B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{861BE73B-06E4-4B1F-A50D-9381DD186150}">
   <dimension ref="A10:N32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -39121,7 +39121,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S1aH1,S2aH1</v>
+        <v>S2aH1,S1aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -39153,7 +39153,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S1aH2,S2aH2</v>
+        <v>S2aH2,S1aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -39249,7 +39249,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B8A2B6A-CB25-49D5-832F-48C41FFBDB2D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{288246FD-69D7-4738-A529-2E80E0FF978B}">
   <dimension ref="A9:G12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -39313,7 +39313,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5D8E4FC-C3EB-49A7-BD13-50B44355A0F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EBE4CD9-0D03-4C8D-BD04-8F26B208690B}">
   <dimension ref="A9:S68"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -39417,7 +39417,7 @@
         <v>178</v>
       </c>
       <c r="R11">
-        <v>0.32229999999999998</v>
+        <v>0.32230000000000003</v>
       </c>
       <c r="S11" t="s">
         <v>179</v>
@@ -39458,7 +39458,7 @@
         <v>180</v>
       </c>
       <c r="R12">
-        <v>0.23194999999999999</v>
+        <v>0.23195000000000002</v>
       </c>
       <c r="S12" t="s">
         <v>179</v>
@@ -39620,7 +39620,7 @@
         <v>180</v>
       </c>
       <c r="R18">
-        <v>0.21781666666666666</v>
+        <v>0.21781666666666669</v>
       </c>
       <c r="S18" t="s">
         <v>179</v>
@@ -39718,7 +39718,7 @@
         <v>178</v>
       </c>
       <c r="R25">
-        <v>0.33420000000000005</v>
+        <v>0.3342</v>
       </c>
       <c r="S25" t="s">
         <v>179</v>
@@ -39760,7 +39760,7 @@
         <v>180</v>
       </c>
       <c r="R28">
-        <v>0.22516666666666665</v>
+        <v>0.22516666666666663</v>
       </c>
       <c r="S28" t="s">
         <v>179</v>
@@ -39816,7 +39816,7 @@
         <v>180</v>
       </c>
       <c r="R32">
-        <v>0.20901666666666666</v>
+        <v>0.20901666666666663</v>
       </c>
       <c r="S32" t="s">
         <v>179</v>
@@ -39830,7 +39830,7 @@
         <v>178</v>
       </c>
       <c r="R33">
-        <v>0.3178833333333333</v>
+        <v>0.31788333333333335</v>
       </c>
       <c r="S33" t="s">
         <v>179</v>
@@ -39858,7 +39858,7 @@
         <v>178</v>
       </c>
       <c r="R35">
-        <v>0.27524999999999999</v>
+        <v>0.27525000000000005</v>
       </c>
       <c r="S35" t="s">
         <v>179</v>
@@ -39872,7 +39872,7 @@
         <v>180</v>
       </c>
       <c r="R36">
-        <v>0.19263333333333332</v>
+        <v>0.19263333333333335</v>
       </c>
       <c r="S36" t="s">
         <v>179</v>
@@ -39886,7 +39886,7 @@
         <v>178</v>
       </c>
       <c r="R37">
-        <v>0.30974999999999997</v>
+        <v>0.30975000000000003</v>
       </c>
       <c r="S37" t="s">
         <v>179</v>
@@ -39900,7 +39900,7 @@
         <v>180</v>
       </c>
       <c r="R38">
-        <v>0.21604999999999999</v>
+        <v>0.21605000000000005</v>
       </c>
       <c r="S38" t="s">
         <v>179</v>
@@ -39984,7 +39984,7 @@
         <v>180</v>
       </c>
       <c r="R44">
-        <v>0.20505000000000004</v>
+        <v>0.20504999999999998</v>
       </c>
       <c r="S44" t="s">
         <v>179</v>
@@ -40012,7 +40012,7 @@
         <v>180</v>
       </c>
       <c r="R46">
-        <v>0.23215</v>
+        <v>0.23214999999999997</v>
       </c>
       <c r="S46" t="s">
         <v>179</v>
@@ -40026,7 +40026,7 @@
         <v>178</v>
       </c>
       <c r="R47">
-        <v>0.37628333333333336</v>
+        <v>0.3762833333333333</v>
       </c>
       <c r="S47" t="s">
         <v>179</v>
@@ -40082,7 +40082,7 @@
         <v>178</v>
       </c>
       <c r="R51">
-        <v>0.40610000000000007</v>
+        <v>0.40609999999999996</v>
       </c>
       <c r="S51" t="s">
         <v>179</v>
@@ -40110,7 +40110,7 @@
         <v>178</v>
       </c>
       <c r="R53">
-        <v>0.35614999999999997</v>
+        <v>0.35615000000000002</v>
       </c>
       <c r="S53" t="s">
         <v>179</v>
@@ -40152,7 +40152,7 @@
         <v>180</v>
       </c>
       <c r="R56">
-        <v>0.24938333333333337</v>
+        <v>0.24938333333333332</v>
       </c>
       <c r="S56" t="s">
         <v>179</v>
@@ -40194,7 +40194,7 @@
         <v>178</v>
       </c>
       <c r="R59">
-        <v>0.39169999999999999</v>
+        <v>0.39169999999999994</v>
       </c>
       <c r="S59" t="s">
         <v>179</v>
@@ -40208,7 +40208,7 @@
         <v>180</v>
       </c>
       <c r="R60">
-        <v>0.28825000000000006</v>
+        <v>0.28825000000000001</v>
       </c>
       <c r="S60" t="s">
         <v>179</v>
@@ -40236,7 +40236,7 @@
         <v>180</v>
       </c>
       <c r="R62">
-        <v>0.23631666666666665</v>
+        <v>0.2363166666666667</v>
       </c>
       <c r="S62" t="s">
         <v>179</v>
@@ -40264,7 +40264,7 @@
         <v>180</v>
       </c>
       <c r="R64">
-        <v>0.21613333333333337</v>
+        <v>0.21613333333333332</v>
       </c>
       <c r="S64" t="s">
         <v>179</v>
@@ -40292,7 +40292,7 @@
         <v>180</v>
       </c>
       <c r="R66">
-        <v>0.23691666666666664</v>
+        <v>0.23691666666666666</v>
       </c>
       <c r="S66" t="s">
         <v>179</v>
@@ -40306,7 +40306,7 @@
         <v>178</v>
       </c>
       <c r="R67">
-        <v>0.3014</v>
+        <v>0.30139999999999995</v>
       </c>
       <c r="S67" t="s">
         <v>179</v>
@@ -40332,7 +40332,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3554B53-70D8-4F4A-A164-FB800CBC03DD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84181807-0894-4ED9-8A83-987A03843FB1}">
   <dimension ref="B9:O146"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -44314,7 +44314,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{623F421D-FBB8-4D80-B170-5B22379C9D27}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9579C299-B62D-4028-8CAF-0A817CEE12BC}">
   <dimension ref="B9:AF86"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -48109,7 +48109,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AED0AAB4-A881-4A2A-81DD-64794209A883}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB260995-3769-47B5-8E81-2E5F9EA3E18B}">
   <dimension ref="A9:S68"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -48254,7 +48254,7 @@
         <v>180</v>
       </c>
       <c r="R12">
-        <v>0.18731666666666669</v>
+        <v>0.18731666666666666</v>
       </c>
       <c r="S12" t="s">
         <v>179</v>
@@ -48376,7 +48376,7 @@
         <v>180</v>
       </c>
       <c r="R16">
-        <v>0.15190000000000001</v>
+        <v>0.15189999999999998</v>
       </c>
       <c r="S16" t="s">
         <v>179</v>
@@ -48794,7 +48794,7 @@
         <v>178</v>
       </c>
       <c r="R45">
-        <v>0.27131666666666671</v>
+        <v>0.27131666666666665</v>
       </c>
       <c r="S45" t="s">
         <v>179</v>
@@ -48892,7 +48892,7 @@
         <v>180</v>
       </c>
       <c r="R52">
-        <v>0.25594999999999996</v>
+        <v>0.25595000000000001</v>
       </c>
       <c r="S52" t="s">
         <v>179</v>
@@ -48920,7 +48920,7 @@
         <v>180</v>
       </c>
       <c r="R54">
-        <v>0.26411666666666672</v>
+        <v>0.26411666666666667</v>
       </c>
       <c r="S54" t="s">
         <v>179</v>
@@ -48948,7 +48948,7 @@
         <v>180</v>
       </c>
       <c r="R56">
-        <v>0.26086666666666669</v>
+        <v>0.26086666666666664</v>
       </c>
       <c r="S56" t="s">
         <v>179</v>
@@ -48962,7 +48962,7 @@
         <v>178</v>
       </c>
       <c r="R57">
-        <v>0.41688333333333327</v>
+        <v>0.41688333333333333</v>
       </c>
       <c r="S57" t="s">
         <v>179</v>
@@ -49018,7 +49018,7 @@
         <v>178</v>
       </c>
       <c r="R61">
-        <v>0.36291666666666661</v>
+        <v>0.36291666666666672</v>
       </c>
       <c r="S61" t="s">
         <v>179</v>
@@ -49032,7 +49032,7 @@
         <v>180</v>
       </c>
       <c r="R62">
-        <v>0.25183333333333335</v>
+        <v>0.2518333333333333</v>
       </c>
       <c r="S62" t="s">
         <v>179</v>
@@ -49128,7 +49128,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D612C4E0-EAC5-45A7-B718-984EA39D894E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAA7931F-5284-4320-B551-77DDC7DC1EC1}">
   <dimension ref="B9:J50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -50214,7 +50214,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30B2F6F5-9D0B-4F1F-88ED-ED47F971A4C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75F268A1-CE31-44F8-A409-6C569C4F49D7}">
   <dimension ref="B9:AF30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -51341,7 +51341,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17830529-FEB7-4378-95AC-0610B77FC375}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21232C37-8F11-433B-BDCC-C4952B9B88F1}">
   <dimension ref="A9:S68"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -51568,7 +51568,7 @@
         <v>180</v>
       </c>
       <c r="R14">
-        <v>0.20638333333333334</v>
+        <v>0.20638333333333336</v>
       </c>
       <c r="S14" t="s">
         <v>179</v>
@@ -51704,7 +51704,7 @@
         <v>180</v>
       </c>
       <c r="R22">
-        <v>0.15886666666666666</v>
+        <v>0.15886666666666668</v>
       </c>
       <c r="S22" t="s">
         <v>179</v>
@@ -51760,7 +51760,7 @@
         <v>180</v>
       </c>
       <c r="R26">
-        <v>0.18118333333333336</v>
+        <v>0.18118333333333334</v>
       </c>
       <c r="S26" t="s">
         <v>179</v>
@@ -51844,7 +51844,7 @@
         <v>180</v>
       </c>
       <c r="R32">
-        <v>0.20483333333333328</v>
+        <v>0.20483333333333334</v>
       </c>
       <c r="S32" t="s">
         <v>179</v>
@@ -51872,7 +51872,7 @@
         <v>180</v>
       </c>
       <c r="R34">
-        <v>0.23810000000000001</v>
+        <v>0.23809999999999998</v>
       </c>
       <c r="S34" t="s">
         <v>179</v>
@@ -51928,7 +51928,7 @@
         <v>180</v>
       </c>
       <c r="R38">
-        <v>0.2203333333333333</v>
+        <v>0.22033333333333335</v>
       </c>
       <c r="S38" t="s">
         <v>179</v>
@@ -51984,7 +51984,7 @@
         <v>180</v>
       </c>
       <c r="R42">
-        <v>0.22556666666666669</v>
+        <v>0.22556666666666667</v>
       </c>
       <c r="S42" t="s">
         <v>179</v>
@@ -52040,7 +52040,7 @@
         <v>180</v>
       </c>
       <c r="R46">
-        <v>0.25499999999999995</v>
+        <v>0.255</v>
       </c>
       <c r="S46" t="s">
         <v>179</v>
@@ -52068,7 +52068,7 @@
         <v>180</v>
       </c>
       <c r="R48">
-        <v>0.19079999999999997</v>
+        <v>0.1908</v>
       </c>
       <c r="S48" t="s">
         <v>179</v>
@@ -52180,7 +52180,7 @@
         <v>180</v>
       </c>
       <c r="R56">
-        <v>0.19996666666666665</v>
+        <v>0.19996666666666671</v>
       </c>
       <c r="S56" t="s">
         <v>179</v>
@@ -52236,7 +52236,7 @@
         <v>180</v>
       </c>
       <c r="R60">
-        <v>0.16086666666666666</v>
+        <v>0.16086666666666669</v>
       </c>
       <c r="S60" t="s">
         <v>179</v>
@@ -52264,7 +52264,7 @@
         <v>180</v>
       </c>
       <c r="R62">
-        <v>0.20025000000000001</v>
+        <v>0.20024999999999996</v>
       </c>
       <c r="S62" t="s">
         <v>179</v>
